--- a/KimTransp.xlsx
+++ b/KimTransp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aulas\5. Projetos TIC - Química - 232\ptic232\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19863E5C-9E79-4EAF-BE1E-E89102311132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445F0E83-7BCC-4413-BA1E-9C3FB7877E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{DF3537CB-6E0A-4E7C-ABFB-B677C0E8847D}"/>
   </bookViews>
@@ -19,6 +19,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Transp!$B$3:$I$3</definedName>
+    <definedName name="Destinos">Transp!$E$4:$E$12</definedName>
+    <definedName name="Fretes">Transp!$K$4:$K$12</definedName>
+    <definedName name="Motoristas">Transp!$I$4:$I$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -348,7 +351,7 @@
     <numFmt numFmtId="164" formatCode="h:mm:ss;@"/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -445,6 +448,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -807,7 +817,7 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -916,6 +926,75 @@
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -928,45 +1007,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -982,35 +1022,18 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1651,20 +1674,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="2:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
       <c r="E2" s="23"/>
       <c r="F2" s="54"/>
       <c r="G2" s="54"/>
@@ -1826,10 +1849,10 @@
       <c r="B11" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="C11" s="64" t="s">
+      <c r="C11" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="64"/>
+      <c r="D11" s="74"/>
       <c r="E11" s="38"/>
       <c r="F11" s="29" t="s">
         <v>45</v>
@@ -1839,10 +1862,10 @@
       <c r="B12" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="65" t="s">
+      <c r="C12" s="75" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="65"/>
+      <c r="D12" s="75"/>
       <c r="E12" s="39"/>
       <c r="F12" s="40" t="s">
         <v>86</v>
@@ -1852,10 +1875,10 @@
       <c r="B13" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="65" t="s">
+      <c r="C13" s="75" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="65"/>
+      <c r="D13" s="75"/>
       <c r="E13" s="39"/>
       <c r="F13" s="40" t="s">
         <v>89</v>
@@ -1865,10 +1888,10 @@
       <c r="B14" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="71" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="61"/>
+      <c r="D14" s="71"/>
       <c r="E14" s="41"/>
       <c r="F14" s="42" t="s">
         <v>92</v>
@@ -1981,18 +2004,18 @@
         <v>28</v>
       </c>
       <c r="F1" s="8"/>
-      <c r="G1" s="69" t="s">
+      <c r="G1" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="68" t="s">
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="69" t="s">
+      <c r="K1" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="L1" s="69"/>
+      <c r="L1" s="51"/>
     </row>
     <row r="2" spans="2:12" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="56"/>
@@ -2002,15 +2025,15 @@
         <v>41</v>
       </c>
       <c r="F2" s="9"/>
-      <c r="G2" s="72" t="str">
+      <c r="G2" s="57" t="str">
         <f ca="1">"Hoje é "&amp;TEXT(TODAY(),"dddd"", dia ""dd"" de ""mmmm"" de ""aaaa")</f>
-        <v>Hoje é quarta-feira, dia 02 de setembro de 2026</v>
-      </c>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="70" t="str">
+        <v>Hoje é quarta-feira, dia 16 de setembro de 2026</v>
+      </c>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="47" t="str">
         <f ca="1">TEXT(NOW(),"hh:mm:ss")</f>
-        <v>18:42:34</v>
+        <v>09:33:07</v>
       </c>
       <c r="K2" s="10">
         <v>80</v>
@@ -2035,22 +2058,22 @@
       <c r="F3" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="67" t="s">
+      <c r="G3" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="71" t="s">
+      <c r="H3" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="67" t="s">
+      <c r="I3" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="67" t="s">
+      <c r="J3" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="67" t="s">
+      <c r="K3" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="67" t="s">
+      <c r="L3" s="45" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2089,7 +2112,7 @@
       <c r="K4" s="22">
         <v>11504.32</v>
       </c>
-      <c r="L4" s="74">
+      <c r="L4" s="49">
         <f>1-J4/K4</f>
         <v>0.65</v>
       </c>
@@ -2129,7 +2152,7 @@
       <c r="K5" s="22">
         <v>6742.6</v>
       </c>
-      <c r="L5" s="75">
+      <c r="L5" s="50">
         <f t="shared" ref="L5:L12" si="3">1-J5/K5</f>
         <v>0.55000000000000004</v>
       </c>
@@ -2169,7 +2192,7 @@
       <c r="K6" s="22">
         <v>13292.5</v>
       </c>
-      <c r="L6" s="74">
+      <c r="L6" s="49">
         <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
@@ -2209,7 +2232,7 @@
       <c r="K7" s="22">
         <v>9465.9699999999993</v>
       </c>
-      <c r="L7" s="74">
+      <c r="L7" s="49">
         <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
@@ -2249,7 +2272,7 @@
       <c r="K8" s="22">
         <v>26574.76</v>
       </c>
-      <c r="L8" s="74">
+      <c r="L8" s="49">
         <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
@@ -2289,7 +2312,7 @@
       <c r="K9" s="22">
         <v>44577.41</v>
       </c>
-      <c r="L9" s="74">
+      <c r="L9" s="49">
         <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
@@ -2329,7 +2352,7 @@
       <c r="K10" s="22">
         <v>15088.51</v>
       </c>
-      <c r="L10" s="74">
+      <c r="L10" s="49">
         <f t="shared" si="3"/>
         <v>0.64999999999999991</v>
       </c>
@@ -2366,10 +2389,10 @@
         <f t="shared" si="2"/>
         <v>11657.806999999999</v>
       </c>
-      <c r="K11" s="66">
+      <c r="K11" s="44">
         <v>33308.019999999997</v>
       </c>
-      <c r="L11" s="74">
+      <c r="L11" s="49">
         <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
@@ -2409,7 +2432,7 @@
       <c r="K12" s="22">
         <v>8530.33</v>
       </c>
-      <c r="L12" s="74">
+      <c r="L12" s="49">
         <f t="shared" si="3"/>
         <v>0.55000000000000004</v>
       </c>
@@ -2419,32 +2442,32 @@
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="59" t="s">
+      <c r="B14" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="60"/>
+      <c r="C14" s="62"/>
       <c r="E14" s="15" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="12"/>
-      <c r="H14" s="57" t="s">
+      <c r="H14" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="I14" s="58"/>
+      <c r="I14" s="60"/>
     </row>
     <row r="15" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="50"/>
-      <c r="C15" s="51"/>
+      <c r="B15" s="79"/>
+      <c r="C15" s="80"/>
       <c r="E15" s="5"/>
       <c r="F15" s="11"/>
       <c r="H15" s="52"/>
       <c r="I15" s="53"/>
     </row>
     <row r="16" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="48" t="s">
+      <c r="B16" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="49"/>
+      <c r="C16" s="64"/>
       <c r="E16" s="17" t="s">
         <v>15</v>
       </c>
@@ -2453,14 +2476,20 @@
       <c r="I16" s="54"/>
     </row>
     <row r="17" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="52"/>
-      <c r="C17" s="53"/>
-      <c r="E17" s="6"/>
+      <c r="B17" s="76">
+        <f>SUMIF(Destinos,B15,Fretes)</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="77"/>
+      <c r="E17" s="78">
+        <f>SUMIF(Motoristas,E15,Fretes)</f>
+        <v>0</v>
+      </c>
       <c r="F17" s="11"/>
-      <c r="H17" s="57" t="s">
+      <c r="H17" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="I17" s="58"/>
+      <c r="I17" s="60"/>
     </row>
     <row r="18" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="54"/>
@@ -2469,10 +2498,10 @@
       <c r="I18" s="53"/>
     </row>
     <row r="19" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="47"/>
+      <c r="C19" s="70"/>
       <c r="E19" s="15" t="s">
         <v>27</v>
       </c>
@@ -2481,41 +2510,41 @@
       <c r="I19" s="54"/>
     </row>
     <row r="20" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="48" t="s">
+      <c r="B20" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="49"/>
+      <c r="C20" s="64"/>
       <c r="E20" s="6"/>
       <c r="F20" s="11"/>
-      <c r="H20" s="57" t="s">
+      <c r="H20" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="I20" s="58"/>
+      <c r="I20" s="60"/>
     </row>
     <row r="21" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="50"/>
-      <c r="C21" s="51"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="66"/>
       <c r="H21" s="52"/>
       <c r="I21" s="53"/>
     </row>
     <row r="22" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="48" t="s">
+      <c r="B22" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="49"/>
+      <c r="C22" s="64"/>
       <c r="E22" s="15" t="s">
         <v>21</v>
       </c>
       <c r="F22" s="12"/>
     </row>
     <row r="23" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="50"/>
-      <c r="C23" s="51"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="66"/>
       <c r="E23" s="7"/>
     </row>
     <row r="24" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="44"/>
-      <c r="C24" s="45"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="68"/>
       <c r="E24" s="16"/>
       <c r="F24" s="11"/>
     </row>
@@ -2528,6 +2557,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="H16:I16"/>
@@ -2544,20 +2580,19 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="2">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{E839BB19-5F09-4525-9529-897BA60ABD8A}">
       <formula1>"Guariroba,Jurupema,Taquaritinga,Vila Negri"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{E8739A41-89D9-4A5B-8841-8BC2682A826B}">
       <formula1>"Baguaçu,Cajobi,Guaraci,Olímpia,Severínia"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15:C15" xr:uid="{5F5EE326-E200-45C9-AC9C-B01677233F19}">
+      <formula1>$E$4:$E$12</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E15" xr:uid="{6293A87B-F521-4E61-9DB2-E4563D533CEC}">
+      <formula1>Motoristas</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/KimTransp.xlsx
+++ b/KimTransp.xlsx
@@ -8,20 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aulas\5. Projetos TIC - Química - 232\ptic232\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445F0E83-7BCC-4413-BA1E-9C3FB7877E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD80F3D9-9D0D-4CD1-96C9-8F573630056A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{DF3537CB-6E0A-4E7C-ABFB-B677C0E8847D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="5" xr2:uid="{DF3537CB-6E0A-4E7C-ABFB-B677C0E8847D}"/>
   </bookViews>
   <sheets>
     <sheet name="Introdução" sheetId="2" r:id="rId1"/>
     <sheet name="Tabela_periódica" sheetId="3" r:id="rId2"/>
-    <sheet name="Transp" sheetId="1" r:id="rId3"/>
+    <sheet name="Gráfico1" sheetId="4" r:id="rId3"/>
+    <sheet name="Gráfico2" sheetId="5" r:id="rId4"/>
+    <sheet name="Gráfico3" sheetId="6" r:id="rId5"/>
+    <sheet name="Transp" sheetId="1" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Transp!$B$3:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Transp!$B$3:$I$3</definedName>
+    <definedName name="Custos">Transp!$J$4:$J$12</definedName>
     <definedName name="Destinos">Transp!$E$4:$E$12</definedName>
+    <definedName name="Estados">Transp!$F$4:$F$12</definedName>
     <definedName name="Fretes">Transp!$K$4:$K$12</definedName>
     <definedName name="Motoristas">Transp!$I$4:$I$12</definedName>
+    <definedName name="Prazo">Transp!$D$4:$D$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="97">
   <si>
     <t>Data Pedido</t>
   </si>
@@ -340,16 +346,20 @@
   </si>
   <si>
     <t>km/h</t>
+  </si>
+  <si>
+    <t>SP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="h:mm:ss;@"/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="171" formatCode="0.000"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -817,7 +827,7 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -832,7 +842,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -947,18 +956,34 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -972,39 +997,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1022,17 +1029,10 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1057,6 +1057,2561 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Transp!$K$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Frete</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Transp!$E$4:$E$12</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Belo Horizonte - MG</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Campinas - SP</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Curitiba - PR</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Goiânia - GO</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Porto Alegre - RS</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Recife - PE</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Rio de Janeiro - RJ</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Salvador - BA</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>São Paulo - SP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Transp!$K$4:$K$12</c:f>
+              <c:numCache>
+                <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>11504.32</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6742.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13292.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9465.9699999999993</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>26574.76</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>44577.41</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15088.51</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>33308.019999999997</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8530.33</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0A53-4E7E-8663-204C62B06379}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1361355183"/>
+        <c:axId val="1281347663"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1361355183"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="_(&quot;R$&quot;* #,##0.00_);_(&quot;R$&quot;* \(#,##0.00\);_(&quot;R$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1281347663"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1281347663"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="_(&quot;R$&quot;* #,##0.00_);_(&quot;R$&quot;* \(#,##0.00\);_(&quot;R$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1361355183"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Transp!$E$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>São Paulo - SP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Transp!$F$3:$F$11</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Estado</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>MG</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SP</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>PR</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>GO</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>RS</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>PE</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>RJ</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>BA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Transp!$F$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-679F-4E53-A556-E8B5F91A8327}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1435291056"/>
+        <c:axId val="1361257743"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1435291056"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1361257743"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1361257743"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1435291056"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Transp!$E$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>São Paulo - SP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Transp!$F$3:$F$11</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Estado</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>MG</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SP</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>PR</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>GO</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>RS</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>PE</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>RJ</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>BA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Transp!$F$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4DB1-4782-971E-78E56F9FA6D7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1435237696"/>
+        <c:axId val="1361248143"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1435237696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1361248143"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1361248143"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1435237696"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{EC88B973-CD9D-490E-8A71-A7FB3EC02F7E}">
+  <sheetPr/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/chartsheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{3F18BBC7-D104-46C8-A09D-4A39CEE2CB37}">
+  <sheetPr/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/chartsheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{879552D5-7EC5-4B95-8B54-581BB257EE72}">
+  <sheetPr/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</chartsheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1293,6 +3848,105 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="9652774" cy="6017012"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D71932BE-346D-CD6B-8EA8-7084C28C53FB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="9652774" cy="6017012"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79D14F44-33E8-B699-9220-309BF077083B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="9652774" cy="6017012"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F65639F-3F94-8D60-FD14-518880C11396}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1674,226 +4328,226 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="72" t="s">
+      <c r="B1" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="2:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="2:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="23"/>
-      <c r="F3" s="27" t="s">
+      <c r="E3" s="22"/>
+      <c r="F3" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="29" t="s">
+      <c r="H3" s="28" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="23"/>
-      <c r="F4" s="30" t="s">
+      <c r="E4" s="22"/>
+      <c r="F4" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="G4" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="H4" s="32" t="s">
+      <c r="H4" s="31" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="23"/>
-      <c r="F5" s="30" t="s">
+      <c r="E5" s="22"/>
+      <c r="F5" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G5" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="32" t="s">
+      <c r="H5" s="31" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="23"/>
-      <c r="F6" s="30" t="s">
+      <c r="E6" s="22"/>
+      <c r="F6" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="G6" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="H6" s="32" t="s">
+      <c r="H6" s="31" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="23"/>
-      <c r="F7" s="30" t="s">
+      <c r="E7" s="22"/>
+      <c r="F7" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="H7" s="32" t="s">
+      <c r="H7" s="31" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="23"/>
-      <c r="F8" s="30" t="s">
+      <c r="E8" s="22"/>
+      <c r="F8" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="G8" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="H8" s="32" t="s">
+      <c r="H8" s="31" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="E9" s="23"/>
-      <c r="F9" s="33" t="s">
+      <c r="E9" s="22"/>
+      <c r="F9" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="G9" s="34" t="s">
+      <c r="G9" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="H9" s="35" t="s">
+      <c r="H9" s="34" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="36"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="37"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="36"/>
     </row>
     <row r="11" spans="2:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C11" s="74" t="s">
+      <c r="C11" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="74"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="29" t="s">
+      <c r="D11" s="73"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="28" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" spans="2:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="75" t="s">
+      <c r="C12" s="74" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="75"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="40" t="s">
+      <c r="D12" s="74"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="39" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="75" t="s">
+      <c r="C13" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="75"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="40" t="s">
+      <c r="D13" s="74"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="39" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="C14" s="71" t="s">
+      <c r="C14" s="70" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="71"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="42" t="s">
+      <c r="D14" s="70"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="41" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1902,22 +4556,22 @@
     <row r="17" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="37"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="43"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="36"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="37"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="36"/>
     </row>
     <row r="21" spans="2:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="37"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="36"/>
     </row>
     <row r="24" spans="2:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="2:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1995,444 +4649,444 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="8" t="s">
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="8"/>
-      <c r="G1" s="51" t="s">
+      <c r="F1" s="7"/>
+      <c r="G1" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="46" t="s">
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="51" t="s">
+      <c r="K1" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="L1" s="51"/>
+      <c r="L1" s="59"/>
     </row>
     <row r="2" spans="2:12" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="18" t="s">
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="57" t="str">
+      <c r="F2" s="8"/>
+      <c r="G2" s="62" t="str">
         <f ca="1">"Hoje é "&amp;TEXT(TODAY(),"dddd"", dia ""dd"" de ""mmmm"" de ""aaaa")</f>
         <v>Hoje é quarta-feira, dia 16 de setembro de 2026</v>
       </c>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="47" t="str">
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="46" t="str">
         <f ca="1">TEXT(NOW(),"hh:mm:ss")</f>
-        <v>09:33:07</v>
-      </c>
-      <c r="K2" s="10">
+        <v>11:06:37</v>
+      </c>
+      <c r="K2" s="9">
         <v>80</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="9" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="45" t="s">
+      <c r="G3" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="48" t="s">
+      <c r="H3" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="45" t="s">
+      <c r="I3" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="45" t="s">
+      <c r="J3" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="45" t="s">
+      <c r="K3" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="45" t="s">
+      <c r="L3" s="44" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="19">
+      <c r="B4" s="18">
         <v>46152</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="18">
         <v>46164</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <f>C4-B4</f>
         <v>12</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="10" t="str">
+      <c r="F4" s="9" t="str">
         <f>RIGHT(E4,2)</f>
         <v>MG</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <v>1272</v>
       </c>
-      <c r="H4" s="10" t="str">
+      <c r="H4" s="9" t="str">
         <f>TEXT((G4/$K$2)/24,"dd"" dia, ""hh"" horas, ""mm"" minutos, ""ss"" segundos""")</f>
         <v>00 dia, 15 horas, 54 minutos, 00 segundos</v>
       </c>
-      <c r="I4" s="20" t="s">
+      <c r="I4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="21">
+      <c r="J4" s="20">
         <f>IF(G4&gt;=1000,K4*35%,K4*45%)</f>
         <v>4026.5119999999997</v>
       </c>
-      <c r="K4" s="22">
+      <c r="K4" s="21">
         <v>11504.32</v>
       </c>
-      <c r="L4" s="49">
+      <c r="L4" s="48">
         <f>1-J4/K4</f>
         <v>0.65</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="19">
+      <c r="B5" s="18">
         <v>46120</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="18">
         <v>46127</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <f>C5-B5</f>
         <v>7</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="10" t="str">
+      <c r="F5" s="9" t="str">
         <f t="shared" ref="F5:F12" si="0">RIGHT(E5,2)</f>
         <v>SP</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="9">
         <v>702</v>
       </c>
-      <c r="H5" s="10" t="str">
+      <c r="H5" s="9" t="str">
         <f t="shared" ref="H5:H12" si="1">TEXT((G5/$K$2)/24,"dd"" dia, ""hh"" horas, ""mm"" minutos, ""ss"" segundos""")</f>
         <v>00 dia, 08 horas, 46 minutos, 30 segundos</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="21">
+      <c r="J5" s="20">
         <f t="shared" ref="J5:J12" si="2">IF(G5&gt;=1000,K5*35%,K5*45%)</f>
         <v>3034.17</v>
       </c>
-      <c r="K5" s="22">
+      <c r="K5" s="21">
         <v>6742.6</v>
       </c>
-      <c r="L5" s="50">
+      <c r="L5" s="49">
         <f t="shared" ref="L5:L12" si="3">1-J5/K5</f>
         <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="19">
+      <c r="B6" s="18">
         <v>46170</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="18">
         <v>46177</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <f t="shared" ref="D6:D12" si="4">C6-B6</f>
         <v>7</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="10" t="str">
+      <c r="F6" s="9" t="str">
         <f t="shared" si="0"/>
         <v>PR</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="9">
         <v>1486</v>
       </c>
-      <c r="H6" s="10" t="str">
+      <c r="H6" s="9" t="str">
         <f t="shared" si="1"/>
         <v>00 dia, 18 horas, 34 minutos, 30 segundos</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="21">
+      <c r="J6" s="20">
         <f>IF(G6&gt;=1000,K6*35%,K6*45%)</f>
         <v>4652.375</v>
       </c>
-      <c r="K6" s="22">
+      <c r="K6" s="21">
         <v>13292.5</v>
       </c>
-      <c r="L6" s="49">
+      <c r="L6" s="48">
         <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="19">
+      <c r="B7" s="18">
         <v>46173</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="18">
         <v>46185</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="10" t="str">
+      <c r="F7" s="9" t="str">
         <f t="shared" si="0"/>
         <v>GO</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="9">
         <v>1028</v>
       </c>
-      <c r="H7" s="10" t="str">
+      <c r="H7" s="9" t="str">
         <f t="shared" si="1"/>
         <v>00 dia, 12 horas, 51 minutos, 00 segundos</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I7" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="21">
+      <c r="J7" s="20">
         <f t="shared" si="2"/>
         <v>3313.0894999999996</v>
       </c>
-      <c r="K7" s="22">
+      <c r="K7" s="21">
         <v>9465.9699999999993</v>
       </c>
-      <c r="L7" s="49">
+      <c r="L7" s="48">
         <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="19">
+      <c r="B8" s="18">
         <v>46072</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="18">
         <v>46083</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="10" t="str">
+      <c r="F8" s="9" t="str">
         <f t="shared" si="0"/>
         <v>RS</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="9">
         <v>3076</v>
       </c>
-      <c r="H8" s="10" t="str">
+      <c r="H8" s="9" t="str">
         <f t="shared" si="1"/>
         <v>01 dia, 14 horas, 27 minutos, 00 segundos</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="J8" s="21">
+      <c r="J8" s="20">
         <f t="shared" si="2"/>
         <v>9301.1659999999993</v>
       </c>
-      <c r="K8" s="22">
+      <c r="K8" s="21">
         <v>26574.76</v>
       </c>
-      <c r="L8" s="49">
+      <c r="L8" s="48">
         <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="19">
+      <c r="B9" s="18">
         <v>46091</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="18">
         <v>46101</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="F9" s="10" t="str">
+      <c r="F9" s="9" t="str">
         <f t="shared" si="0"/>
         <v>PE</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="9">
         <v>5231</v>
       </c>
-      <c r="H9" s="10" t="str">
+      <c r="H9" s="9" t="str">
         <f t="shared" si="1"/>
         <v>02 dia, 17 horas, 23 minutos, 15 segundos</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="I9" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="21">
+      <c r="J9" s="20">
         <f t="shared" si="2"/>
         <v>15602.093500000001</v>
       </c>
-      <c r="K9" s="22">
+      <c r="K9" s="21">
         <v>44577.41</v>
       </c>
-      <c r="L9" s="49">
+      <c r="L9" s="48">
         <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="19">
+      <c r="B10" s="18">
         <v>46075</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="18">
         <v>46080</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="10" t="str">
+      <c r="F10" s="9" t="str">
         <f t="shared" si="0"/>
         <v>RJ</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="9">
         <v>1701</v>
       </c>
-      <c r="H10" s="10" t="str">
+      <c r="H10" s="9" t="str">
         <f t="shared" si="1"/>
         <v>00 dia, 21 horas, 15 minutos, 45 segundos</v>
       </c>
-      <c r="I10" s="20" t="s">
+      <c r="I10" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="J10" s="21">
+      <c r="J10" s="20">
         <f t="shared" si="2"/>
         <v>5280.9785000000002</v>
       </c>
-      <c r="K10" s="22">
+      <c r="K10" s="21">
         <v>15088.51</v>
       </c>
-      <c r="L10" s="49">
+      <c r="L10" s="48">
         <f t="shared" si="3"/>
         <v>0.64999999999999991</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="19">
+      <c r="B11" s="18">
         <v>46068</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="18">
         <v>46078</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="10" t="str">
+      <c r="F11" s="9" t="str">
         <f t="shared" si="0"/>
         <v>BA</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="9">
         <v>3882</v>
       </c>
-      <c r="H11" s="10" t="str">
+      <c r="H11" s="9" t="str">
         <f t="shared" si="1"/>
         <v>02 dia, 00 horas, 31 minutos, 30 segundos</v>
       </c>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="21">
+      <c r="J11" s="20">
         <f t="shared" si="2"/>
         <v>11657.806999999999</v>
       </c>
-      <c r="K11" s="44">
+      <c r="K11" s="43">
         <v>33308.019999999997</v>
       </c>
-      <c r="L11" s="49">
+      <c r="L11" s="48">
         <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="19">
+      <c r="B12" s="18">
         <v>46186</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="18">
         <v>46198</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="10" t="str">
+      <c r="F12" s="9" t="str">
         <f t="shared" si="0"/>
         <v>SP</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="9">
         <v>916</v>
       </c>
-      <c r="H12" s="10" t="str">
+      <c r="H12" s="9" t="str">
         <f t="shared" si="1"/>
         <v>00 dia, 11 horas, 27 minutos, 00 segundos</v>
       </c>
-      <c r="I12" s="20" t="s">
+      <c r="I12" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="J12" s="21">
+      <c r="J12" s="20">
         <f t="shared" si="2"/>
         <v>3838.6485000000002</v>
       </c>
-      <c r="K12" s="22">
+      <c r="K12" s="21">
         <v>8530.33</v>
       </c>
-      <c r="L12" s="49">
+      <c r="L12" s="48">
         <f t="shared" si="3"/>
         <v>0.55000000000000004</v>
       </c>
@@ -2442,111 +5096,126 @@
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="61" t="s">
+      <c r="B14" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="62"/>
-      <c r="E14" s="15" t="s">
+      <c r="C14" s="65"/>
+      <c r="E14" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="12"/>
-      <c r="H14" s="59" t="s">
+      <c r="F14" s="11"/>
+      <c r="I14" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="I14" s="60"/>
     </row>
     <row r="15" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="79"/>
-      <c r="C15" s="80"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="67"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="11"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="53"/>
+      <c r="F15" s="10"/>
+      <c r="I15" s="77">
+        <f>SUM(Custos)</f>
+        <v>60706.840000000004</v>
+      </c>
     </row>
     <row r="16" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="63" t="s">
+      <c r="B16" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="64"/>
-      <c r="E16" s="17" t="s">
+      <c r="C16" s="57"/>
+      <c r="E16" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="12"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="54"/>
+      <c r="F16" s="11"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
     </row>
     <row r="17" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="76">
+      <c r="B17" s="68">
         <f>SUMIF(Destinos,B15,Fretes)</f>
         <v>0</v>
       </c>
-      <c r="C17" s="77"/>
-      <c r="E17" s="78">
+      <c r="C17" s="69"/>
+      <c r="E17" s="50">
         <f>SUMIF(Motoristas,E15,Fretes)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="11"/>
-      <c r="H17" s="59" t="s">
+      <c r="F17" s="10"/>
+      <c r="I17" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="I17" s="60"/>
     </row>
     <row r="18" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="53"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="51"/>
+      <c r="I18" s="77">
+        <f>AVERAGE(Custos)</f>
+        <v>6745.2044444444446</v>
+      </c>
     </row>
     <row r="19" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="69" t="s">
+      <c r="B19" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="70"/>
-      <c r="E19" s="15" t="s">
+      <c r="C19" s="55"/>
+      <c r="E19" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="12"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="54"/>
+      <c r="F19" s="11"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
     </row>
     <row r="20" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="63" t="s">
+      <c r="B20" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="64"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="11"/>
-      <c r="H20" s="59" t="s">
+      <c r="C20" s="57"/>
+      <c r="E20" s="75">
+        <f>AVERAGE(Prazo)</f>
+        <v>9.5555555555555554</v>
+      </c>
+      <c r="F20" s="10"/>
+      <c r="I20" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="I20" s="60"/>
     </row>
     <row r="21" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="65"/>
-      <c r="C21" s="66"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="53"/>
+      <c r="B21" s="78">
+        <v>46023</v>
+      </c>
+      <c r="C21" s="58"/>
+      <c r="I21" s="77">
+        <f>SUM(Fretes)</f>
+        <v>169084.41999999998</v>
+      </c>
     </row>
     <row r="22" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="63" t="s">
+      <c r="B22" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="64"/>
-      <c r="E22" s="15" t="s">
+      <c r="C22" s="57"/>
+      <c r="E22" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="12"/>
+      <c r="F22" s="11"/>
     </row>
     <row r="23" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="65"/>
-      <c r="C23" s="66"/>
-      <c r="E23" s="7"/>
+      <c r="B23" s="78">
+        <v>46053</v>
+      </c>
+      <c r="C23" s="58"/>
+      <c r="E23" s="6" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="24" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="67"/>
-      <c r="C24" s="68"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="11"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="53"/>
+      <c r="E24" s="15">
+        <f>AVERAGEIF(Estados,E23,Prazo)</f>
+        <v>9.5</v>
+      </c>
+      <c r="F24" s="10"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26"/>
@@ -2556,7 +5225,17 @@
       <c r="B33"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="17">
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B19:C19"/>
@@ -2564,24 +5243,8 @@
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B17:C17"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{E839BB19-5F09-4525-9529-897BA60ABD8A}">
       <formula1>"Guariroba,Jurupema,Taquaritinga,Vila Negri"</formula1>
     </dataValidation>
@@ -2593,6 +5256,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E15" xr:uid="{6293A87B-F521-4E61-9DB2-E4563D533CEC}">
       <formula1>Motoristas</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E23" xr:uid="{BE3585EE-559B-49E8-BF98-88EDB084A924}">
+      <formula1>Estados</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
